--- a/Data/RemapDrafts/AyakaRemapDraft.xlsx
+++ b/Data/RemapDrafts/AyakaRemapDraft.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer\Games\Genshin\Repos\Repos\Fix-Raiden-Boss\Data\RemapDrafts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0E710E-1699-4618-9811-6EFCAC2FDA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB7DD67-1576-4D70-881F-1F9B25666230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{28D9F790-F783-48FD-BEB4-7CBDC2AAB951}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="1" xr2:uid="{28D9F790-F783-48FD-BEB4-7CBDC2AAB951}"/>
   </bookViews>
   <sheets>
-    <sheet name="V4.0 - Ayaka to SpringBloom" sheetId="1" r:id="rId1"/>
-    <sheet name="V4.0 - SpringBloom to Ayaka" sheetId="2" r:id="rId2"/>
+    <sheet name="Credits" sheetId="3" r:id="rId1"/>
+    <sheet name="V4.0 - Ayaka to SpringBloom" sheetId="1" r:id="rId2"/>
+    <sheet name="V4.0 - SpringBloom to Ayaka" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V4.0 - Ayaka to SpringBloom'!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.0 - SpringBloom to Ayaka'!$A$1:$D$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.0 - Ayaka to SpringBloom'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'V4.0 - SpringBloom to Ayaka'!$A$1:$D$115</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>Uncertainty</t>
   </si>
@@ -215,13 +216,22 @@
   </si>
   <si>
     <t>AyakaSpringBloom's top left dress</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>AlbertGold#2696</t>
+  </si>
+  <si>
+    <t>Authors</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,6 +242,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -255,14 +281,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -615,17 +645,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702E3278-8B0E-45CC-A4F5-509017C72F7E}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="26" x14ac:dyDescent="0.6">
+      <c r="A1" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{E5170200-D154-4E90-A370-5B2EAEB96110}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C4E70-BE98-42D0-8822-2C2538E5BC03}">
   <dimension ref="A1:D119"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="107.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1796875" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" customWidth="1"/>
+    <col min="4" max="4" width="107.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -639,7 +700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -647,7 +708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -655,7 +716,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -663,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -671,7 +732,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -685,7 +746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -699,7 +760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -713,7 +774,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -727,7 +788,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -735,7 +796,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -743,7 +804,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -757,7 +818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -771,7 +832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -785,7 +846,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -799,7 +860,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -813,7 +874,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -821,7 +882,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -829,7 +890,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -837,7 +898,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -845,7 +906,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -853,7 +914,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -864,7 +925,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -872,7 +933,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -880,7 +941,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -888,7 +949,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -902,7 +963,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -916,7 +977,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -924,7 +985,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -932,7 +993,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -940,7 +1001,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -948,7 +1009,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -962,7 +1023,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -976,7 +1037,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -987,7 +1048,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -995,7 +1056,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1003,7 +1064,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1011,7 +1072,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1022,7 +1083,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1030,7 +1091,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1038,7 +1099,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1046,7 +1107,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1054,7 +1115,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1062,7 +1123,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1070,7 +1131,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1078,7 +1139,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1089,7 +1150,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1097,7 +1158,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1105,7 +1166,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1113,7 +1174,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1121,7 +1182,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1129,7 +1190,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1137,7 +1198,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1145,7 +1206,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1156,7 +1217,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1170,7 +1231,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -1181,7 +1242,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -1192,7 +1253,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1203,7 +1264,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1214,7 +1275,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -1225,7 +1286,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -1239,7 +1300,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1247,7 +1308,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -1255,7 +1316,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -1263,7 +1324,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1271,7 +1332,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1282,7 +1343,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -1293,7 +1354,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -1304,7 +1365,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -1315,7 +1376,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -1326,7 +1387,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -1337,7 +1398,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -1348,7 +1409,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -1359,7 +1420,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -1367,7 +1428,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -1375,7 +1436,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -1383,7 +1444,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -1391,7 +1452,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -1399,7 +1460,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -1407,7 +1468,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -1415,7 +1476,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -1423,7 +1484,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -1431,7 +1492,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -1439,7 +1500,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -1447,7 +1508,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -1455,7 +1516,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -1463,7 +1524,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -1471,7 +1532,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
@@ -1479,7 +1540,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>87</v>
       </c>
@@ -1490,7 +1551,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>88</v>
       </c>
@@ -1501,7 +1562,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>89</v>
       </c>
@@ -1509,7 +1570,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>90</v>
       </c>
@@ -1517,7 +1578,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>91</v>
       </c>
@@ -1528,7 +1589,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>92</v>
       </c>
@@ -1536,7 +1597,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>93</v>
       </c>
@@ -1547,7 +1608,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>94</v>
       </c>
@@ -1558,7 +1619,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>95</v>
       </c>
@@ -1566,7 +1627,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>96</v>
       </c>
@@ -1574,7 +1635,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>97</v>
       </c>
@@ -1582,7 +1643,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>98</v>
       </c>
@@ -1590,7 +1651,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>99</v>
       </c>
@@ -1598,7 +1659,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>100</v>
       </c>
@@ -1606,7 +1667,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>101</v>
       </c>
@@ -1614,7 +1675,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>102</v>
       </c>
@@ -1622,7 +1683,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>103</v>
       </c>
@@ -1630,7 +1691,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>104</v>
       </c>
@@ -1638,7 +1699,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>105</v>
       </c>
@@ -1646,7 +1707,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>106</v>
       </c>
@@ -1654,7 +1715,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>107</v>
       </c>
@@ -1662,7 +1723,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>108</v>
       </c>
@@ -1670,7 +1731,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>109</v>
       </c>
@@ -1678,7 +1739,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>110</v>
       </c>
@@ -1686,7 +1747,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>111</v>
       </c>
@@ -1697,7 +1758,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>112</v>
       </c>
@@ -1705,7 +1766,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>113</v>
       </c>
@@ -1716,7 +1777,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>114</v>
       </c>
@@ -1727,7 +1788,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>115</v>
       </c>
@@ -1735,7 +1796,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>116</v>
       </c>
@@ -1743,7 +1804,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>117</v>
       </c>
@@ -1761,18 +1822,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BB2CA9B-FACB-4A51-AE97-1A7E4C39BBD5}">
   <dimension ref="A1:D115"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="75.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.7265625" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="75.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1786,7 +1847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1794,7 +1855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1805,7 +1866,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1813,7 +1874,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1827,7 +1888,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1838,7 +1899,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1849,7 +1910,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1860,7 +1921,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1868,7 +1929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1882,7 +1943,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1890,7 +1951,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1898,7 +1959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1906,7 +1967,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1914,7 +1975,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1922,7 +1983,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1930,7 +1991,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1938,7 +1999,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1952,7 +2013,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1960,7 +2021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1968,7 +2029,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1982,7 +2043,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1993,7 +2054,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2004,7 +2065,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2012,7 +2073,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2026,7 +2087,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2037,7 +2098,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2048,7 +2109,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2059,7 +2120,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2070,7 +2131,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2078,7 +2139,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -2086,7 +2147,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2094,7 +2155,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2102,7 +2163,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -2110,7 +2171,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -2118,7 +2179,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -2126,7 +2187,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -2134,7 +2195,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -2142,7 +2203,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -2150,7 +2211,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -2158,7 +2219,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -2166,7 +2227,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -2177,7 +2238,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -2185,7 +2246,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -2193,7 +2254,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -2201,7 +2262,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -2212,7 +2273,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -2220,7 +2281,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -2228,7 +2289,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -2236,7 +2297,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -2247,7 +2308,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -2255,7 +2316,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -2263,7 +2324,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -2271,7 +2332,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -2282,7 +2343,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -2290,7 +2351,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -2298,7 +2359,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -2306,7 +2367,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -2317,7 +2378,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -2325,7 +2386,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -2333,7 +2394,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -2341,7 +2402,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -2349,7 +2410,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -2357,7 +2418,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -2365,7 +2426,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -2373,7 +2434,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -2381,7 +2442,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -2389,7 +2450,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -2397,7 +2458,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -2405,7 +2466,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -2413,7 +2474,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -2421,7 +2482,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -2429,7 +2490,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -2437,7 +2498,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -2445,7 +2506,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -2453,7 +2514,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -2461,7 +2522,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -2469,7 +2530,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -2477,7 +2538,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -2485,7 +2546,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -2493,7 +2554,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -2501,7 +2562,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -2509,7 +2570,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -2517,7 +2578,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -2525,7 +2586,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -2533,7 +2594,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -2541,7 +2602,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -2549,7 +2610,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
@@ -2563,7 +2624,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>87</v>
       </c>
@@ -2574,7 +2635,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>88</v>
       </c>
@@ -2582,7 +2643,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>89</v>
       </c>
@@ -2590,7 +2651,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>90</v>
       </c>
@@ -2598,7 +2659,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>91</v>
       </c>
@@ -2606,7 +2667,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>92</v>
       </c>
@@ -2614,7 +2675,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>93</v>
       </c>
@@ -2622,7 +2683,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>94</v>
       </c>
@@ -2630,7 +2691,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>95</v>
       </c>
@@ -2638,7 +2699,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>96</v>
       </c>
@@ -2646,7 +2707,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>97</v>
       </c>
@@ -2654,7 +2715,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>98</v>
       </c>
@@ -2662,7 +2723,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>99</v>
       </c>
@@ -2670,7 +2731,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>100</v>
       </c>
@@ -2678,7 +2739,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>101</v>
       </c>
@@ -2686,7 +2747,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>102</v>
       </c>
@@ -2694,7 +2755,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>103</v>
       </c>
@@ -2702,7 +2763,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>104</v>
       </c>
@@ -2710,7 +2771,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>105</v>
       </c>
@@ -2718,7 +2779,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>106</v>
       </c>
@@ -2726,7 +2787,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>107</v>
       </c>
@@ -2734,7 +2795,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>108</v>
       </c>
@@ -2742,7 +2803,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>109</v>
       </c>
@@ -2750,7 +2811,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>110</v>
       </c>
@@ -2764,7 +2825,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>111</v>
       </c>
@@ -2772,7 +2833,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>112</v>
       </c>
@@ -2780,7 +2841,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>113</v>
       </c>
